--- a/Implementation_SRF.xlsx
+++ b/Implementation_SRF.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20325"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{8453584B-0AC3-4674-A65B-6A950F1A329E}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{49197008-B8A1-42C5-8C65-708A89CE260B}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3846" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="185">
   <si>
     <t>#</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Company</t>
-  </si>
-  <si>
-    <t>Fixed</t>
   </si>
   <si>
     <t>Business</t>
@@ -162,9 +159,6 @@
     <t>Upload</t>
   </si>
   <si>
-    <t>9-Point Declaration shall be in PDF or Image Document duly signed</t>
-  </si>
-  <si>
     <t>PO No.</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
     <t>Fixed Term | Fixed Term With Auto - Renewal | Not Applicable | Perpetual</t>
   </si>
   <si>
-    <t>Refer the table - Colum H and Column I</t>
-  </si>
-  <si>
     <t>Initial Renewal Date</t>
   </si>
   <si>
@@ -607,6 +598,46 @@
   </si>
   <si>
     <t>Agro | Commercial | General | Pharma | Semi-Speciality</t>
+  </si>
+  <si>
+    <t>9-Point Declaration shall be in PDF or Image Document duly signed, Mandatory document</t>
+  </si>
+  <si>
+    <t>Request Title</t>
+  </si>
+  <si>
+    <t>Draft Type</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Counterparty Template | No Templatel </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>|</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+Standard Template</t>
+    </r>
+  </si>
+  <si>
+    <t>SRF Limited</t>
+  </si>
+  <si>
+    <t>SCB</t>
   </si>
 </sst>
 </file>
@@ -830,7 +861,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -898,14 +929,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -914,6 +939,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -933,6 +967,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1216,14 +1253,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AU87"/>
+  <dimension ref="A1:AU89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="5" customWidth="1"/>
     <col min="2" max="2" width="24" style="5" customWidth="1"/>
     <col min="3" max="3" width="20.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="4.5703125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="25" style="5" customWidth="1"/>
     <col min="6" max="6" width="15" style="5" customWidth="1"/>
     <col min="7" max="7" width="5.42578125" style="5" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="5"/>
@@ -1249,293 +1286,296 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="U1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>171</v>
-      </c>
-      <c r="AS1" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="AT1" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="AU1" s="3" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
+      <c r="A2" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+      <c r="A3" s="23">
+        <v>1</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23" t="s">
+        <v>8</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>183</v>
+      </c>
       <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1662,20 +1702,19 @@
     </row>
     <row r="5" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6" t="s">
-        <v>178</v>
+      <c r="E5" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>7</v>
@@ -1802,20 +1841,21 @@
       </c>
     </row>
     <row r="6" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>175</v>
+      </c>
       <c r="G6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1942,10 +1982,10 @@
     </row>
     <row r="7" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>6</v>
@@ -2081,10 +2121,10 @@
     </row>
     <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>6</v>
@@ -2220,10 +2260,10 @@
     </row>
     <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>6</v>
@@ -2358,22 +2398,20 @@
       </c>
     </row>
     <row r="10" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6" t="s">
-        <v>179</v>
-      </c>
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2500,22 +2538,19 @@
     </row>
     <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>180</v>
+        <v>11</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>7</v>
@@ -2643,20 +2678,19 @@
     </row>
     <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6" t="s">
-        <v>181</v>
+      <c r="D12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>7</v>
@@ -2784,22 +2818,19 @@
     </row>
     <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>12</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>24</v>
+        <v>11</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>7</v>
@@ -2927,21 +2958,23 @@
     </row>
     <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>13</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="9"/>
+      <c r="B14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="G14" s="1" t="s">
         <v>7</v>
       </c>
@@ -3068,21 +3101,21 @@
     </row>
     <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="6"/>
+        <v>19</v>
+      </c>
+      <c r="F15" s="9"/>
       <c r="G15" s="1" t="s">
         <v>7</v>
       </c>
@@ -3209,23 +3242,21 @@
     </row>
     <row r="16" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>15</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>30</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="1" t="s">
         <v>7</v>
       </c>
@@ -3352,21 +3383,21 @@
     </row>
     <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
+        <v>14</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>181</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="12" t="s">
-        <v>33</v>
-      </c>
+      <c r="E17" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="1" t="s">
         <v>7</v>
       </c>
@@ -3493,21 +3524,23 @@
     </row>
     <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>17</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="F18" s="16"/>
+        <v>15</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>29</v>
+      </c>
       <c r="G18" s="1" t="s">
         <v>7</v>
       </c>
@@ -3524,7 +3557,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>7</v>
@@ -3634,20 +3667,20 @@
     </row>
     <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>18</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>35</v>
+        <v>16</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="12" t="s">
-        <v>36</v>
+        <v>179</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>7</v>
@@ -3775,21 +3808,21 @@
     </row>
     <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="12" t="s">
-        <v>38</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F20" s="16"/>
       <c r="G20" s="1" t="s">
         <v>7</v>
       </c>
@@ -3916,19 +3949,21 @@
     </row>
     <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="E21" s="9"/>
-      <c r="F21" s="16"/>
+      <c r="F21" s="12" t="s">
+        <v>34</v>
+      </c>
       <c r="G21" s="1" t="s">
         <v>7</v>
       </c>
@@ -3936,7 +3971,7 @@
         <v>7</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
@@ -4055,19 +4090,21 @@
     </row>
     <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="E22" s="9"/>
-      <c r="F22" s="16"/>
+      <c r="F22" s="12" t="s">
+        <v>36</v>
+      </c>
       <c r="G22" s="1" t="s">
         <v>7</v>
       </c>
@@ -4193,24 +4230,20 @@
       </c>
     </row>
     <row r="23" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A23" s="9">
-        <v>22</v>
+      <c r="A23" s="6">
+        <v>20</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>44</v>
-      </c>
+      <c r="E23" s="9"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="1" t="s">
         <v>7</v>
       </c>
@@ -4335,15 +4368,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="28"/>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>21</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="9"/>
+      <c r="F24" s="16"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -4469,23 +4508,23 @@
       </c>
     </row>
     <row r="25" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
-        <v>1</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>8</v>
+      <c r="A25" s="9">
+        <v>22</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>7</v>
@@ -4611,25 +4650,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
-        <v>2</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>51</v>
-      </c>
+    <row r="26" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="25"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="26"/>
       <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
@@ -4756,22 +4785,22 @@
     </row>
     <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>3</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="12" t="s">
-        <v>53</v>
+      <c r="F27" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>7</v>
@@ -4899,23 +4928,21 @@
     </row>
     <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>8</v>
-      </c>
+      <c r="E28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="18"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -5042,22 +5069,22 @@
     </row>
     <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>8</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>7</v>
@@ -5185,13 +5212,13 @@
     </row>
     <row r="30" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
@@ -5326,15 +5353,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>5</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="G31" s="1" t="s">
         <v>7</v>
       </c>
@@ -5461,20 +5498,22 @@
     </row>
     <row r="32" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>1</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="19" t="s">
-        <v>61</v>
+      <c r="B32" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>7</v>
@@ -5600,23 +5639,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
-        <v>2</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="19" t="s">
-        <v>61</v>
-      </c>
+    <row r="33" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="26"/>
       <c r="G33" s="1" t="s">
         <v>7</v>
       </c>
@@ -5743,10 +5774,10 @@
     </row>
     <row r="34" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>6</v>
@@ -5756,7 +5787,7 @@
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>7</v>
@@ -5884,10 +5915,10 @@
     </row>
     <row r="35" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>6</v>
@@ -5897,7 +5928,7 @@
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>7</v>
@@ -6025,10 +6056,10 @@
     </row>
     <row r="36" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>6</v>
@@ -6038,7 +6069,7 @@
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>7</v>
@@ -6166,20 +6197,20 @@
     </row>
     <row r="37" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>7</v>
@@ -6307,10 +6338,10 @@
     </row>
     <row r="38" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>6</v>
@@ -6320,7 +6351,7 @@
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>7</v>
@@ -6448,20 +6479,20 @@
     </row>
     <row r="39" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>7</v>
@@ -6589,10 +6620,10 @@
     </row>
     <row r="40" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>6</v>
@@ -6602,7 +6633,7 @@
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>7</v>
@@ -6730,10 +6761,10 @@
     </row>
     <row r="41" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>6</v>
@@ -6743,7 +6774,7 @@
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>7</v>
@@ -6871,20 +6902,20 @@
     </row>
     <row r="42" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>7</v>
@@ -7012,20 +7043,20 @@
     </row>
     <row r="43" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>67</v>
+        <v>7</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>7</v>
@@ -7052,7 +7083,7 @@
         <v>7</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>7</v>
@@ -7153,20 +7184,20 @@
     </row>
     <row r="44" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>7</v>
@@ -7292,15 +7323,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
+    <row r="45" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>12</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="F45" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="G45" s="1" t="s">
         <v>7</v>
       </c>
@@ -7427,20 +7466,20 @@
     </row>
     <row r="46" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C46" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>7</v>
@@ -7491,7 +7530,7 @@
         <v>7</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="X46" s="1" t="s">
         <v>7</v>
@@ -7566,23 +7605,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
-        <v>2</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E47" s="6"/>
-      <c r="F47" s="19" t="s">
-        <v>61</v>
-      </c>
+    <row r="47" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B47" s="25"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="26"/>
       <c r="G47" s="1" t="s">
         <v>7</v>
       </c>
@@ -7709,7 +7740,7 @@
     </row>
     <row r="48" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>73</v>
@@ -7718,11 +7749,11 @@
         <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>7</v>
@@ -7850,20 +7881,20 @@
     </row>
     <row r="49" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="19" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>7</v>
@@ -7989,15 +8020,23 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="28"/>
+    <row r="50" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>3</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="6"/>
+      <c r="F50" s="19" t="s">
+        <v>58</v>
+      </c>
       <c r="G50" s="1" t="s">
         <v>7</v>
       </c>
@@ -8011,7 +8050,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>7</v>
@@ -8124,22 +8163,20 @@
     </row>
     <row r="51" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>8</v>
+        <v>64</v>
+      </c>
+      <c r="E51" s="6"/>
+      <c r="F51" s="19" t="s">
+        <v>58</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>7</v>
@@ -8265,23 +8302,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
-        <v>2</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F52" s="6"/>
+    <row r="52" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="26"/>
       <c r="G52" s="1" t="s">
         <v>7</v>
       </c>
@@ -8301,7 +8330,7 @@
         <v>7</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>7</v>
@@ -8328,7 +8357,7 @@
         <v>7</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="W52" s="1" t="s">
         <v>7</v>
@@ -8408,10 +8437,10 @@
     </row>
     <row r="53" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>6</v>
@@ -8419,8 +8448,12 @@
       <c r="D53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
+      <c r="E53" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="G53" s="1" t="s">
         <v>7</v>
       </c>
@@ -8547,18 +8580,20 @@
     </row>
     <row r="54" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>4</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>84</v>
+        <v>2</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="6"/>
+      <c r="E54" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="F54" s="6"/>
       <c r="G54" s="1" t="s">
         <v>7</v>
@@ -8686,20 +8721,18 @@
     </row>
     <row r="55" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>5</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>85</v>
+        <v>3</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>86</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="6"/>
       <c r="F55" s="6"/>
       <c r="G55" s="1" t="s">
         <v>7</v>
@@ -8827,26 +8860,24 @@
     </row>
     <row r="56" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>6</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>16</v>
+        <v>4</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>81</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="E56" s="6"/>
-      <c r="F56" s="12" t="s">
-        <v>87</v>
-      </c>
+      <c r="F56" s="6"/>
       <c r="G56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>7</v>
@@ -8968,23 +8999,23 @@
     </row>
     <row r="57" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>7</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>17</v>
+        <v>5</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="F57" s="12" t="s">
-        <v>88</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" s="6"/>
       <c r="G57" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>7</v>
@@ -9109,20 +9140,20 @@
     </row>
     <row r="58" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="12" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>7</v>
@@ -9250,20 +9281,20 @@
     </row>
     <row r="59" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>7</v>
@@ -9391,20 +9422,20 @@
     </row>
     <row r="60" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>7</v>
@@ -9532,24 +9563,26 @@
     </row>
     <row r="61" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
+      <c r="F61" s="12" t="s">
+        <v>89</v>
+      </c>
       <c r="G61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>7</v>
@@ -9671,20 +9704,20 @@
     </row>
     <row r="62" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="12" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>7</v>
@@ -9812,23 +9845,19 @@
     </row>
     <row r="63" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>97</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
       <c r="G63" s="1" t="s">
         <v>7</v>
       </c>
@@ -9955,20 +9984,20 @@
     </row>
     <row r="64" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>7</v>
@@ -10096,22 +10125,22 @@
     </row>
     <row r="65" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>7</v>
@@ -10239,20 +10268,20 @@
     </row>
     <row r="66" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="12" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>7</v>
@@ -10378,15 +10407,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="33"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="34"/>
+    <row r="67" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>15</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F67" s="12" t="s">
+        <v>94</v>
+      </c>
       <c r="G67" s="1" t="s">
         <v>7</v>
       </c>
@@ -10513,21 +10552,21 @@
     </row>
     <row r="68" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="F68" s="20"/>
+        <v>33</v>
+      </c>
+      <c r="E68" s="6"/>
+      <c r="F68" s="12" t="s">
+        <v>98</v>
+      </c>
       <c r="G68" s="1" t="s">
         <v>7</v>
       </c>
@@ -10652,159 +10691,73 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
-        <v>2</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU69" s="1" t="s">
-        <v>7</v>
-      </c>
+    <row r="69" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="34"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+      <c r="AC69" s="1"/>
+      <c r="AD69" s="1"/>
+      <c r="AE69" s="1"/>
+      <c r="AF69" s="1"/>
+      <c r="AG69" s="1"/>
+      <c r="AH69" s="1"/>
+      <c r="AI69" s="1"/>
+      <c r="AJ69" s="1"/>
+      <c r="AK69" s="1"/>
+      <c r="AL69" s="1"/>
+      <c r="AM69" s="1"/>
+      <c r="AN69" s="1"/>
+      <c r="AO69" s="1"/>
+      <c r="AP69" s="1"/>
+      <c r="AQ69" s="1"/>
+      <c r="AR69" s="1"/>
+      <c r="AS69" s="1"/>
+      <c r="AT69" s="1"/>
+      <c r="AU69" s="1"/>
     </row>
     <row r="70" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E70" s="6"/>
+      <c r="E70" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="F70" s="20"/>
       <c r="G70" s="1" t="s">
         <v>7</v>
@@ -10932,13 +10885,13 @@
     </row>
     <row r="71" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>7</v>
@@ -11070,20 +11023,20 @@
       </c>
     </row>
     <row r="72" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A72" s="14">
-        <v>5</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
+      <c r="A72" s="6">
+        <v>3</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E72" s="6"/>
+      <c r="F72" s="20"/>
       <c r="G72" s="1" t="s">
         <v>7</v>
       </c>
@@ -11209,712 +11162,624 @@
       </c>
     </row>
     <row r="73" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A73" s="14">
+      <c r="A73" s="6">
+        <v>4</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" s="6"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU73" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A74" s="14">
+        <v>5</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C74" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B73" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="C73" s="14" t="s">
+      <c r="D74" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU74" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A75" s="14">
         <v>6</v>
       </c>
-      <c r="D73" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
-      <c r="G73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU73" s="1" t="s">
+      <c r="B75" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU75" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="74" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="25"/>
-      <c r="G74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU74" s="1" t="s">
+    <row r="76" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="29"/>
+      <c r="G76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU76" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="75" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="26" t="s">
-        <v>115</v>
-      </c>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU75" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A76" s="6">
-        <v>1</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU76" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
-        <v>2</v>
-      </c>
-      <c r="B77" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="P77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="T77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="W77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="X77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Y77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Z77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AM77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AN77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AO77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AP77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AQ77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AS77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AT77" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="AU77" s="1" t="s">
-        <v>7</v>
-      </c>
+    <row r="77" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="25"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
+      <c r="AC77" s="1"/>
+      <c r="AD77" s="1"/>
+      <c r="AE77" s="1"/>
+      <c r="AF77" s="1"/>
+      <c r="AG77" s="1"/>
+      <c r="AH77" s="1"/>
+      <c r="AI77" s="1"/>
+      <c r="AJ77" s="1"/>
+      <c r="AK77" s="1"/>
+      <c r="AL77" s="1"/>
+      <c r="AM77" s="1"/>
+      <c r="AN77" s="1"/>
+      <c r="AO77" s="1"/>
+      <c r="AP77" s="1"/>
+      <c r="AQ77" s="1"/>
+      <c r="AR77" s="1"/>
+      <c r="AS77" s="1"/>
+      <c r="AT77" s="1"/>
+      <c r="AU77" s="1"/>
     </row>
     <row r="78" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E78" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="F78" s="12" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>7</v>
@@ -12042,20 +11907,22 @@
     </row>
     <row r="79" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E79" s="6"/>
+        <v>33</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>8</v>
+      </c>
       <c r="F79" s="12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>7</v>
@@ -12183,20 +12050,20 @@
     </row>
     <row r="80" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="12" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>7</v>
@@ -12324,20 +12191,20 @@
     </row>
     <row r="81" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="12" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>7</v>
@@ -12385,7 +12252,7 @@
         <v>7</v>
       </c>
       <c r="V81" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>7</v>
@@ -12465,20 +12332,20 @@
     </row>
     <row r="82" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>7</v>
@@ -12606,19 +12473,21 @@
     </row>
     <row r="83" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="E83" s="20"/>
-      <c r="F83" s="20"/>
+        <v>31</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E83" s="6"/>
+      <c r="F83" s="12" t="s">
+        <v>124</v>
+      </c>
       <c r="G83" s="1" t="s">
         <v>7</v>
       </c>
@@ -12745,19 +12614,21 @@
     </row>
     <row r="84" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>9</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>109</v>
+        <v>7</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D84" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
+        <v>31</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E84" s="6"/>
+      <c r="F84" s="12" t="s">
+        <v>126</v>
+      </c>
       <c r="G84" s="1" t="s">
         <v>7</v>
       </c>
@@ -12884,16 +12755,16 @@
     </row>
     <row r="85" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>10</v>
-      </c>
-      <c r="B85" s="22" t="s">
-        <v>175</v>
+        <v>8</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D85" s="21" t="s">
-        <v>67</v>
+        <v>31</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
@@ -13023,16 +12894,16 @@
     </row>
     <row r="86" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
@@ -13162,16 +13033,16 @@
     </row>
     <row r="87" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
@@ -13299,16 +13170,294 @@
         <v>7</v>
       </c>
     </row>
+    <row r="88" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>11</v>
+      </c>
+      <c r="B88" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D88" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU88" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>12</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D89" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="E89" s="20"/>
+      <c r="F89" s="20"/>
+      <c r="G89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="V89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="X89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AM89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AN89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AQ89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AS89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AT89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AU89" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A76:F76"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Implementation_SRF.xlsx
+++ b/Implementation_SRF.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20325"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{49197008-B8A1-42C5-8C65-708A89CE260B}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{25A57D58-D147-4F1D-9FA3-22FCA046517A}" xr6:coauthVersionLast="34" xr6:coauthVersionMax="34" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3854" uniqueCount="187">
   <si>
     <t>#</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Initial Renewal Date</t>
   </si>
   <si>
-    <t>This field will be shown and will be mandatory when Contract Term is selected as Fixed Term With Auto - Renewal</t>
-  </si>
-  <si>
     <t>Contract Expiration Date</t>
   </si>
   <si>
@@ -638,6 +635,15 @@
   </si>
   <si>
     <t>SCB</t>
+  </si>
+  <si>
+    <t>Dependent Upon #28, Open this field if Selection = Fixed Term With Auto - Renewal</t>
+  </si>
+  <si>
+    <t>Counterparty Registered Office Address</t>
+  </si>
+  <si>
+    <t>Counterparty Corporate Office Address</t>
   </si>
 </sst>
 </file>
@@ -932,6 +938,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -967,9 +976,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1286,145 +1292,145 @@
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="AU1" s="3" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32"/>
+      <c r="A2" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="33"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="23">
         <v>1</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C3" s="23" t="s">
         <v>6</v>
@@ -1437,127 +1443,127 @@
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AG3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AL3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AM3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AN3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AO3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AU3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:47" x14ac:dyDescent="0.25">
@@ -1574,7 +1580,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>7</v>
@@ -1714,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>7</v>
@@ -1854,7 +1860,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>7</v>
@@ -2550,7 +2556,7 @@
         <v>7</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>7</v>
@@ -2690,7 +2696,7 @@
         <v>7</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>7</v>
@@ -2830,7 +2836,7 @@
         <v>7</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>7</v>
@@ -3385,8 +3391,8 @@
       <c r="A17" s="6">
         <v>14</v>
       </c>
-      <c r="B17" s="36" t="s">
-        <v>181</v>
+      <c r="B17" s="24" t="s">
+        <v>180</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>11</v>
@@ -3395,7 +3401,7 @@
         <v>7</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F17" s="6"/>
       <c r="G17" s="1" t="s">
@@ -3557,7 +3563,7 @@
         <v>7</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>7</v>
@@ -3680,7 +3686,7 @@
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>7</v>
@@ -3811,7 +3817,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>11</v>
@@ -3820,7 +3826,7 @@
         <v>7</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="1" t="s">
@@ -3971,7 +3977,7 @@
         <v>7</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>7</v>
@@ -4651,14 +4657,14 @@
       </c>
     </row>
     <row r="26" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+      <c r="A26" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
       <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
@@ -5084,7 +5090,7 @@
         <v>8</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>7</v>
@@ -5215,10 +5221,10 @@
         <v>4</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>52</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>7</v>
@@ -5358,7 +5364,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>45</v>
@@ -5370,7 +5376,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>7</v>
@@ -5501,7 +5507,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>6</v>
@@ -5640,14 +5646,14 @@
       </c>
     </row>
     <row r="33" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24" t="s">
-        <v>56</v>
-      </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="26"/>
+      <c r="A33" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="27"/>
       <c r="G33" s="1" t="s">
         <v>7</v>
       </c>
@@ -5777,7 +5783,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>6</v>
@@ -5787,7 +5793,7 @@
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>7</v>
@@ -5918,7 +5924,7 @@
         <v>2</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>6</v>
@@ -5928,7 +5934,7 @@
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>7</v>
@@ -6059,7 +6065,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>6</v>
@@ -6069,7 +6075,7 @@
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>7</v>
@@ -6200,7 +6206,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>6</v>
@@ -6210,7 +6216,7 @@
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>7</v>
@@ -6341,7 +6347,7 @@
         <v>5</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>6</v>
@@ -6351,7 +6357,7 @@
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>7</v>
@@ -6482,17 +6488,17 @@
         <v>6</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>7</v>
@@ -6623,7 +6629,7 @@
         <v>7</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>6</v>
@@ -6633,7 +6639,7 @@
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>7</v>
@@ -6764,7 +6770,7 @@
         <v>8</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>6</v>
@@ -6774,7 +6780,7 @@
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>7</v>
@@ -6905,7 +6911,7 @@
         <v>9</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>6</v>
@@ -6915,7 +6921,7 @@
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>7</v>
@@ -7046,7 +7052,7 @@
         <v>10</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>6</v>
@@ -7056,7 +7062,7 @@
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>7</v>
@@ -7083,7 +7089,7 @@
         <v>7</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>7</v>
@@ -7187,17 +7193,17 @@
         <v>11</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>7</v>
@@ -7328,17 +7334,17 @@
         <v>12</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>7</v>
@@ -7469,17 +7475,17 @@
         <v>13</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>7</v>
@@ -7530,7 +7536,7 @@
         <v>7</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X46" s="1" t="s">
         <v>7</v>
@@ -7606,14 +7612,14 @@
       </c>
     </row>
     <row r="47" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="25"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="26"/>
+      <c r="A47" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="27"/>
       <c r="G47" s="1" t="s">
         <v>7</v>
       </c>
@@ -7743,17 +7749,17 @@
         <v>1</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>7</v>
@@ -7884,17 +7890,17 @@
         <v>2</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>7</v>
@@ -8025,17 +8031,17 @@
         <v>3</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>7</v>
@@ -8050,7 +8056,7 @@
         <v>7</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>7</v>
@@ -8166,17 +8172,17 @@
         <v>4</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>7</v>
@@ -8303,14 +8309,14 @@
       </c>
     </row>
     <row r="52" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="26"/>
+      <c r="A52" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="27"/>
       <c r="G52" s="1" t="s">
         <v>7</v>
       </c>
@@ -8330,7 +8336,7 @@
         <v>7</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>7</v>
@@ -8357,7 +8363,7 @@
         <v>7</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W52" s="1" t="s">
         <v>7</v>
@@ -8440,7 +8446,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>6</v>
@@ -8583,7 +8589,7 @@
         <v>2</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>11</v>
@@ -8592,7 +8598,7 @@
         <v>7</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F54" s="6"/>
       <c r="G54" s="1" t="s">
@@ -8724,7 +8730,7 @@
         <v>3</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>6</v>
@@ -8863,7 +8869,7 @@
         <v>4</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>6</v>
@@ -8877,7 +8883,7 @@
         <v>7</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>7</v>
@@ -9002,20 +9008,20 @@
         <v>5</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F57" s="6"/>
       <c r="G57" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>7</v>
@@ -9143,7 +9149,7 @@
         <v>6</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>6</v>
@@ -9153,7 +9159,7 @@
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>7</v>
@@ -9284,7 +9290,7 @@
         <v>7</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>6</v>
@@ -9294,7 +9300,7 @@
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>7</v>
@@ -9425,7 +9431,7 @@
         <v>8</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>6</v>
@@ -9435,7 +9441,7 @@
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>7</v>
@@ -9566,7 +9572,7 @@
         <v>9</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>6</v>
@@ -9576,13 +9582,13 @@
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>7</v>
@@ -9707,7 +9713,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>6</v>
@@ -9717,7 +9723,7 @@
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>7</v>
@@ -9848,7 +9854,7 @@
         <v>11</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>6</v>
@@ -9987,7 +9993,7 @@
         <v>12</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>6</v>
@@ -9997,7 +10003,7 @@
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>7</v>
@@ -10128,7 +10134,7 @@
         <v>13</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>11</v>
@@ -10137,10 +10143,10 @@
         <v>33</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>7</v>
@@ -10271,7 +10277,7 @@
         <v>14</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>6</v>
@@ -10281,7 +10287,7 @@
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>7</v>
@@ -10412,7 +10418,7 @@
         <v>15</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>11</v>
@@ -10421,10 +10427,10 @@
         <v>33</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>7</v>
@@ -10555,7 +10561,7 @@
         <v>16</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>6</v>
@@ -10565,7 +10571,7 @@
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>7</v>
@@ -10692,14 +10698,14 @@
       </c>
     </row>
     <row r="69" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="35"/>
+      <c r="A69" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="36"/>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -10747,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>47</v>
@@ -10756,7 +10762,7 @@
         <v>7</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F70" s="20"/>
       <c r="G70" s="1" t="s">
@@ -10888,7 +10894,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>6</v>
@@ -11027,10 +11033,10 @@
         <v>3</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>7</v>
@@ -11166,10 +11172,10 @@
         <v>4</v>
       </c>
       <c r="B73" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>7</v>
@@ -11305,13 +11311,13 @@
         <v>5</v>
       </c>
       <c r="B74" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C74" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E74" s="14"/>
       <c r="F74" s="14"/>
@@ -11444,13 +11450,13 @@
         <v>6</v>
       </c>
       <c r="B75" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C75" s="14" t="s">
         <v>6</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E75" s="14"/>
       <c r="F75" s="14"/>
@@ -11579,14 +11585,14 @@
       </c>
     </row>
     <row r="76" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="29"/>
+      <c r="A76" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="29"/>
+      <c r="F76" s="30"/>
       <c r="G76" s="1" t="s">
         <v>7</v>
       </c>
@@ -11712,14 +11718,14 @@
       </c>
     </row>
     <row r="77" spans="1:47" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="25"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="26"/>
+      <c r="A77" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="27"/>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -11767,7 +11773,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>31</v>
@@ -11779,7 +11785,7 @@
         <v>8</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>7</v>
@@ -11910,7 +11916,7 @@
         <v>2</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>31</v>
@@ -11922,7 +11928,7 @@
         <v>8</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>7</v>
@@ -12053,7 +12059,7 @@
         <v>3</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>31</v>
@@ -12063,7 +12069,7 @@
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>7</v>
@@ -12194,7 +12200,7 @@
         <v>4</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>31</v>
@@ -12204,7 +12210,7 @@
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>7</v>
@@ -12252,7 +12258,7 @@
         <v>7</v>
       </c>
       <c r="V81" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>7</v>
@@ -12335,7 +12341,7 @@
         <v>5</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>31</v>
@@ -12345,7 +12351,7 @@
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>7</v>
@@ -12476,7 +12482,7 @@
         <v>6</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>31</v>
@@ -12486,7 +12492,7 @@
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>7</v>
@@ -12617,7 +12623,7 @@
         <v>7</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>31</v>
@@ -12627,7 +12633,7 @@
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>7</v>
@@ -12758,13 +12764,13 @@
         <v>8</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E85" s="20"/>
       <c r="F85" s="20"/>
@@ -12897,13 +12903,13 @@
         <v>9</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E86" s="20"/>
       <c r="F86" s="20"/>
@@ -13036,13 +13042,13 @@
         <v>10</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D87" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E87" s="20"/>
       <c r="F87" s="20"/>
@@ -13175,13 +13181,13 @@
         <v>11</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D88" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E88" s="20"/>
       <c r="F88" s="20"/>
@@ -13314,13 +13320,13 @@
         <v>12</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D89" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E89" s="20"/>
       <c r="F89" s="20"/>
